--- a/Escopo/Escopo-modelo.xlsx
+++ b/Escopo/Escopo-modelo.xlsx
@@ -96,7 +96,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Quando nenhum resultado depende de medição, ou a medição não exige rastreabilidade a padrões.</t>
+          <t xml:space="preserve">Quando a rastreabilidade não é requisito, e só no 7.1.5.2. O 7.1.5.1 vale sempre que há monitoramento ou medição.</t>
         </r>
       </text>
     </comment>
@@ -132,7 +132,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Quando não há nenhuma atividade depois da entrega: garantia, troca, assistência, reclamação.</t>
+          <t xml:space="preserve">Quando não há nenhuma atividade depois da entrega: garantia, troca, assistência técnica, manutenção.</t>
         </r>
       </text>
     </comment>
@@ -204,13 +204,13 @@
     <t xml:space="preserve">Pode não se aplicar</t>
   </si>
   <si>
-    <t xml:space="preserve">Os requisitos 7.1.5, 8.3, 8.5.3 e 8.5.5. Podem ser declarados não aplicáveis, com justificativa, se a ausência não afetar o cliente.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aplica-se sempre</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Todos os outros. Marcar “Não” neles gera o aviso “requisito que se aplica sempre”.</t>
+    <t xml:space="preserve">Os candidatos mais comuns: a rastreabilidade do 7.1.5 (o 7.1.5.2), o 8.3, o 8.5.3 e o 8.5.5. Podem ser declarados não aplicáveis, com justificativa, se a ausência não afetar o cliente.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quase sempre se aplica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Todos os outros. Marcar “Não” neles pede uma justificativa reforçada, e a conferência mostra o aviso “justificativa reforçada”, que não conta como erro.</t>
   </si>
   <si>
     <t xml:space="preserve">Exclusão indevida</t>
@@ -840,7 +840,7 @@
     <t xml:space="preserve">Não aplicáveis que se aplicam</t>
   </si>
   <si>
-    <t xml:space="preserve">Exclusão indevida, ou requisito que se aplica sempre.</t>
+    <t xml:space="preserve">Exclusão indevida: a ausência afeta o cliente.</t>
   </si>
   <si>
     <t xml:space="preserve">Requisitos a decidir ou completar</t>
@@ -1014,7 +1014,7 @@
     <t xml:space="preserve">Pizzas e bebidas, servidas no salão, para retirada no balcão e entregues em casa. Encomendas para eventos.</t>
   </si>
   <si>
-    <t xml:space="preserve">Registrar o pedido, produzir e embalar, entregar; planejar e dirigir a loja, medir e melhorar; comprar e armazenar, manter equipamentos e motos, treinar a equipe.</t>
+    <t xml:space="preserve">Registrar o pedido, produzir e embalar, entregar, atender no salão; planejar e dirigir a loja, medir e melhorar; comprar e armazenar, manter equipamentos e motos, treinar a equipe.</t>
   </si>
   <si>
     <t xml:space="preserve">Pagamento pelo aplicativo, controle de pragas e manutenção do forno, por empresas contratadas.</t>
@@ -1092,7 +1092,10 @@
     <t xml:space="preserve">Processos e riscos</t>
   </si>
   <si>
-    <t xml:space="preserve">O mapa de processos está na parede da cozinha. Os riscos são revistos uma vez por ano.</t>
+    <t xml:space="preserve">O mapa de processos está na parede da cozinha. Os riscos são revistos a cada seis meses.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Semestral</t>
   </si>
   <si>
     <t xml:space="preserve">Matriz de riscos</t>
@@ -1146,9 +1149,6 @@
     <t xml:space="preserve">Pede um ciclo PDCA por semestre e acompanha o resultado.</t>
   </si>
   <si>
-    <t xml:space="preserve">Semestral</t>
-  </si>
-  <si>
     <t xml:space="preserve">PDCA dos atrasos na entrega</t>
   </si>
   <si>
@@ -1224,7 +1224,7 @@
     <t xml:space="preserve">Mapa de processos e matrizes de riscos</t>
   </si>
   <si>
-    <t xml:space="preserve">Aprovou o medidor de espessura de R$ 96.000, e a instalação atrasou.</t>
+    <t xml:space="preserve">Aprovou os dois medidores de espessura em linha, de R$ 96.000, com instalação até 30/06/2027; em maio, a compra ainda não tinha sido feita.</t>
   </si>
   <si>
     <t xml:space="preserve">Acompanhar a instalação na reunião mensal de resultados.</t>
@@ -1839,11 +1839,11 @@
         </c:ser>
         <c:gapWidth val="80"/>
         <c:overlap val="0"/>
-        <c:axId val="27346000"/>
-        <c:axId val="88855004"/>
+        <c:axId val="14773113"/>
+        <c:axId val="13339635"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="27346000"/>
+        <c:axId val="14773113"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1875,7 +1875,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="88855004"/>
+        <c:crossAx val="13339635"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1883,7 +1883,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="88855004"/>
+        <c:axId val="13339635"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -1923,7 +1923,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="27346000"/>
+        <c:crossAx val="14773113"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="2"/>
@@ -2241,7 +2241,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="4" t="s">
         <v>14</v>
       </c>
@@ -2587,7 +2587,7 @@
         <v>73</v>
       </c>
       <c r="C17" s="14" t="str">
-        <f aca="false">IF(C4="","Escreva a organização",IF(COUNTIF(D5:D12,"OK")&lt;5,"Há campo obrigatório em branco",IF(COUNTIF(Aplicabilidade!H7:H51,"Exclusão indevida")+COUNTIF(Aplicabilidade!H7:H51,"Requisito que se aplica sempre")&gt;0,"Há requisito declarado não aplicável que se aplica",IF(SUMPRODUCT((Aplicabilidade!H7:H51&lt;&gt;"OK")*1)&gt;0,"Há requisito a decidir ou a completar na aba Aplicabilidade","OK"))))</f>
+        <f aca="false">IF(C4="","Escreva a organização",IF(COUNTIF(D5:D12,"OK")&lt;5,"Há campo obrigatório em branco",IF(COUNTIF(Aplicabilidade!H7:H51,"Exclusão indevida")&gt;0,"Há requisito declarado não aplicável que se aplica",IF(SUMPRODUCT((Aplicabilidade!H7:H51&lt;&gt;"OK")*(Aplicabilidade!H7:H51&lt;&gt;"Justificativa reforçada: requisito fora dos candidatos comuns"))&gt;0,"Há requisito a decidir ou a completar na aba Aplicabilidade","OK"))))</f>
         <v>Escreva a organização</v>
       </c>
       <c r="D17" s="14"/>
@@ -2751,7 +2751,7 @@
       <c r="F7" s="5"/>
       <c r="G7" s="19"/>
       <c r="H7" s="9" t="str">
-        <f aca="false">IF(E7="","Falta decidir",IF(E7="Sim","OK",IF(D7="Aplica-se sempre","Requisito que se aplica sempre",IF(F7="","Falta a justificativa",IF(G7="","Falta avaliar o efeito",IF(G7="Sim","Exclusão indevida","OK"))))))</f>
+        <f aca="false">IF(E7="","Falta decidir",IF(E7="Sim","OK",IF(F7="","Falta a justificativa",IF(G7="","Falta avaliar o efeito",IF(G7="Sim","Exclusão indevida",IF(D7="Quase sempre se aplica","Justificativa reforçada: requisito fora dos candidatos comuns","OK"))))))</f>
         <v>Falta decidir</v>
       </c>
     </row>
@@ -2769,7 +2769,7 @@
       <c r="F8" s="5"/>
       <c r="G8" s="19"/>
       <c r="H8" s="9" t="str">
-        <f aca="false">IF(E8="","Falta decidir",IF(E8="Sim","OK",IF(D8="Aplica-se sempre","Requisito que se aplica sempre",IF(F8="","Falta a justificativa",IF(G8="","Falta avaliar o efeito",IF(G8="Sim","Exclusão indevida","OK"))))))</f>
+        <f aca="false">IF(E8="","Falta decidir",IF(E8="Sim","OK",IF(F8="","Falta a justificativa",IF(G8="","Falta avaliar o efeito",IF(G8="Sim","Exclusão indevida",IF(D8="Quase sempre se aplica","Justificativa reforçada: requisito fora dos candidatos comuns","OK"))))))</f>
         <v>Falta decidir</v>
       </c>
     </row>
@@ -2787,7 +2787,7 @@
       <c r="F9" s="5"/>
       <c r="G9" s="19"/>
       <c r="H9" s="9" t="str">
-        <f aca="false">IF(E9="","Falta decidir",IF(E9="Sim","OK",IF(D9="Aplica-se sempre","Requisito que se aplica sempre",IF(F9="","Falta a justificativa",IF(G9="","Falta avaliar o efeito",IF(G9="Sim","Exclusão indevida","OK"))))))</f>
+        <f aca="false">IF(E9="","Falta decidir",IF(E9="Sim","OK",IF(F9="","Falta a justificativa",IF(G9="","Falta avaliar o efeito",IF(G9="Sim","Exclusão indevida",IF(D9="Quase sempre se aplica","Justificativa reforçada: requisito fora dos candidatos comuns","OK"))))))</f>
         <v>Falta decidir</v>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
       <c r="F10" s="5"/>
       <c r="G10" s="19"/>
       <c r="H10" s="9" t="str">
-        <f aca="false">IF(E10="","Falta decidir",IF(E10="Sim","OK",IF(D10="Aplica-se sempre","Requisito que se aplica sempre",IF(F10="","Falta a justificativa",IF(G10="","Falta avaliar o efeito",IF(G10="Sim","Exclusão indevida","OK"))))))</f>
+        <f aca="false">IF(E10="","Falta decidir",IF(E10="Sim","OK",IF(F10="","Falta a justificativa",IF(G10="","Falta avaliar o efeito",IF(G10="Sim","Exclusão indevida",IF(D10="Quase sempre se aplica","Justificativa reforçada: requisito fora dos candidatos comuns","OK"))))))</f>
         <v>Falta decidir</v>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       <c r="F11" s="5"/>
       <c r="G11" s="19"/>
       <c r="H11" s="9" t="str">
-        <f aca="false">IF(E11="","Falta decidir",IF(E11="Sim","OK",IF(D11="Aplica-se sempre","Requisito que se aplica sempre",IF(F11="","Falta a justificativa",IF(G11="","Falta avaliar o efeito",IF(G11="Sim","Exclusão indevida","OK"))))))</f>
+        <f aca="false">IF(E11="","Falta decidir",IF(E11="Sim","OK",IF(F11="","Falta a justificativa",IF(G11="","Falta avaliar o efeito",IF(G11="Sim","Exclusão indevida",IF(D11="Quase sempre se aplica","Justificativa reforçada: requisito fora dos candidatos comuns","OK"))))))</f>
         <v>Falta decidir</v>
       </c>
     </row>
@@ -2841,7 +2841,7 @@
       <c r="F12" s="5"/>
       <c r="G12" s="19"/>
       <c r="H12" s="9" t="str">
-        <f aca="false">IF(E12="","Falta decidir",IF(E12="Sim","OK",IF(D12="Aplica-se sempre","Requisito que se aplica sempre",IF(F12="","Falta a justificativa",IF(G12="","Falta avaliar o efeito",IF(G12="Sim","Exclusão indevida","OK"))))))</f>
+        <f aca="false">IF(E12="","Falta decidir",IF(E12="Sim","OK",IF(F12="","Falta a justificativa",IF(G12="","Falta avaliar o efeito",IF(G12="Sim","Exclusão indevida",IF(D12="Quase sempre se aplica","Justificativa reforçada: requisito fora dos candidatos comuns","OK"))))))</f>
         <v>Falta decidir</v>
       </c>
     </row>
@@ -2859,7 +2859,7 @@
       <c r="F13" s="5"/>
       <c r="G13" s="19"/>
       <c r="H13" s="9" t="str">
-        <f aca="false">IF(E13="","Falta decidir",IF(E13="Sim","OK",IF(D13="Aplica-se sempre","Requisito que se aplica sempre",IF(F13="","Falta a justificativa",IF(G13="","Falta avaliar o efeito",IF(G13="Sim","Exclusão indevida","OK"))))))</f>
+        <f aca="false">IF(E13="","Falta decidir",IF(E13="Sim","OK",IF(F13="","Falta a justificativa",IF(G13="","Falta avaliar o efeito",IF(G13="Sim","Exclusão indevida",IF(D13="Quase sempre se aplica","Justificativa reforçada: requisito fora dos candidatos comuns","OK"))))))</f>
         <v>Falta decidir</v>
       </c>
     </row>
@@ -2877,7 +2877,7 @@
       <c r="F14" s="5"/>
       <c r="G14" s="19"/>
       <c r="H14" s="9" t="str">
-        <f aca="false">IF(E14="","Falta decidir",IF(E14="Sim","OK",IF(D14="Aplica-se sempre","Requisito que se aplica sempre",IF(F14="","Falta a justificativa",IF(G14="","Falta avaliar o efeito",IF(G14="Sim","Exclusão indevida","OK"))))))</f>
+        <f aca="false">IF(E14="","Falta decidir",IF(E14="Sim","OK",IF(F14="","Falta a justificativa",IF(G14="","Falta avaliar o efeito",IF(G14="Sim","Exclusão indevida",IF(D14="Quase sempre se aplica","Justificativa reforçada: requisito fora dos candidatos comuns","OK"))))))</f>
         <v>Falta decidir</v>
       </c>
     </row>
@@ -2895,7 +2895,7 @@
       <c r="F15" s="5"/>
       <c r="G15" s="19"/>
       <c r="H15" s="9" t="str">
-        <f aca="false">IF(E15="","Falta decidir",IF(E15="Sim","OK",IF(D15="Aplica-se sempre","Requisito que se aplica sempre",IF(F15="","Falta a justificativa",IF(G15="","Falta avaliar o efeito",IF(G15="Sim","Exclusão indevida","OK"))))))</f>
+        <f aca="false">IF(E15="","Falta decidir",IF(E15="Sim","OK",IF(F15="","Falta a justificativa",IF(G15="","Falta avaliar o efeito",IF(G15="Sim","Exclusão indevida",IF(D15="Quase sempre se aplica","Justificativa reforçada: requisito fora dos candidatos comuns","OK"))))))</f>
         <v>Falta decidir</v>
       </c>
     </row>
@@ -2913,7 +2913,7 @@
       <c r="F16" s="5"/>
       <c r="G16" s="19"/>
       <c r="H16" s="9" t="str">
-        <f aca="false">IF(E16="","Falta decidir",IF(E16="Sim","OK",IF(D16="Aplica-se sempre","Requisito que se aplica sempre",IF(F16="","Falta a justificativa",IF(G16="","Falta avaliar o efeito",IF(G16="Sim","Exclusão indevida","OK"))))))</f>
+        <f aca="false">IF(E16="","Falta decidir",IF(E16="Sim","OK",IF(F16="","Falta a justificativa",IF(G16="","Falta avaliar o efeito",IF(G16="Sim","Exclusão indevida",IF(D16="Quase sempre se aplica","Justificativa reforçada: requisito fora dos candidatos comuns","OK"))))))</f>
         <v>Falta decidir</v>
       </c>
     </row>
@@ -2931,7 +2931,7 @@
       <c r="F17" s="5"/>
       <c r="G17" s="19"/>
       <c r="H17" s="9" t="str">
-        <f aca="false">IF(E17="","Falta decidir",IF(E17="Sim","OK",IF(D17="Aplica-se sempre","Requisito que se aplica sempre",IF(F17="","Falta a justificativa",IF(G17="","Falta avaliar o efeito",IF(G17="Sim","Exclusão indevida","OK"))))))</f>
+        <f aca="false">IF(E17="","Falta decidir",IF(E17="Sim","OK",IF(F17="","Falta a justificativa",IF(G17="","Falta avaliar o efeito",IF(G17="Sim","Exclusão indevida",IF(D17="Quase sempre se aplica","Justificativa reforçada: requisito fora dos candidatos comuns","OK"))))))</f>
         <v>Falta decidir</v>
       </c>
     </row>
@@ -2949,7 +2949,7 @@
       <c r="F18" s="5"/>
       <c r="G18" s="19"/>
       <c r="H18" s="9" t="str">
-        <f aca="false">IF(E18="","Falta decidir",IF(E18="Sim","OK",IF(D18="Aplica-se sempre","Requisito que se aplica sempre",IF(F18="","Falta a justificativa",IF(G18="","Falta avaliar o efeito",IF(G18="Sim","Exclusão indevida","OK"))))))</f>
+        <f aca="false">IF(E18="","Falta decidir",IF(E18="Sim","OK",IF(F18="","Falta a justificativa",IF(G18="","Falta avaliar o efeito",IF(G18="Sim","Exclusão indevida",IF(D18="Quase sempre se aplica","Justificativa reforçada: requisito fora dos candidatos comuns","OK"))))))</f>
         <v>Falta decidir</v>
       </c>
     </row>
@@ -2967,7 +2967,7 @@
       <c r="F19" s="5"/>
       <c r="G19" s="19"/>
       <c r="H19" s="9" t="str">
-        <f aca="false">IF(E19="","Falta decidir",IF(E19="Sim","OK",IF(D19="Aplica-se sempre","Requisito que se aplica sempre",IF(F19="","Falta a justificativa",IF(G19="","Falta avaliar o efeito",IF(G19="Sim","Exclusão indevida","OK"))))))</f>
+        <f aca="false">IF(E19="","Falta decidir",IF(E19="Sim","OK",IF(F19="","Falta a justificativa",IF(G19="","Falta avaliar o efeito",IF(G19="Sim","Exclusão indevida",IF(D19="Quase sempre se aplica","Justificativa reforçada: requisito fora dos candidatos comuns","OK"))))))</f>
         <v>Falta decidir</v>
       </c>
     </row>
@@ -2985,7 +2985,7 @@
       <c r="F20" s="5"/>
       <c r="G20" s="19"/>
       <c r="H20" s="9" t="str">
-        <f aca="false">IF(E20="","Falta decidir",IF(E20="Sim","OK",IF(D20="Aplica-se sempre","Requisito que se aplica sempre",IF(F20="","Falta a justificativa",IF(G20="","Falta avaliar o efeito",IF(G20="Sim","Exclusão indevida","OK"))))))</f>
+        <f aca="false">IF(E20="","Falta decidir",IF(E20="Sim","OK",IF(F20="","Falta a justificativa",IF(G20="","Falta avaliar o efeito",IF(G20="Sim","Exclusão indevida",IF(D20="Quase sempre se aplica","Justificativa reforçada: requisito fora dos candidatos comuns","OK"))))))</f>
         <v>Falta decidir</v>
       </c>
     </row>
@@ -3003,7 +3003,7 @@
       <c r="F21" s="5"/>
       <c r="G21" s="19"/>
       <c r="H21" s="9" t="str">
-        <f aca="false">IF(E21="","Falta decidir",IF(E21="Sim","OK",IF(D21="Aplica-se sempre","Requisito que se aplica sempre",IF(F21="","Falta a justificativa",IF(G21="","Falta avaliar o efeito",IF(G21="Sim","Exclusão indevida","OK"))))))</f>
+        <f aca="false">IF(E21="","Falta decidir",IF(E21="Sim","OK",IF(F21="","Falta a justificativa",IF(G21="","Falta avaliar o efeito",IF(G21="Sim","Exclusão indevida",IF(D21="Quase sempre se aplica","Justificativa reforçada: requisito fora dos candidatos comuns","OK"))))))</f>
         <v>Falta decidir</v>
       </c>
     </row>
@@ -3021,7 +3021,7 @@
       <c r="F22" s="5"/>
       <c r="G22" s="19"/>
       <c r="H22" s="9" t="str">
-        <f aca="false">IF(E22="","Falta decidir",IF(E22="Sim","OK",IF(D22="Aplica-se sempre","Requisito que se aplica sempre",IF(F22="","Falta a justificativa",IF(G22="","Falta avaliar o efeito",IF(G22="Sim","Exclusão indevida","OK"))))))</f>
+        <f aca="false">IF(E22="","Falta decidir",IF(E22="Sim","OK",IF(F22="","Falta a justificativa",IF(G22="","Falta avaliar o efeito",IF(G22="Sim","Exclusão indevida",IF(D22="Quase sempre se aplica","Justificativa reforçada: requisito fora dos candidatos comuns","OK"))))))</f>
         <v>Falta decidir</v>
       </c>
     </row>
@@ -3039,7 +3039,7 @@
       <c r="F23" s="5"/>
       <c r="G23" s="19"/>
       <c r="H23" s="9" t="str">
-        <f aca="false">IF(E23="","Falta decidir",IF(E23="Sim","OK",IF(D23="Aplica-se sempre","Requisito que se aplica sempre",IF(F23="","Falta a justificativa",IF(G23="","Falta avaliar o efeito",IF(G23="Sim","Exclusão indevida","OK"))))))</f>
+        <f aca="false">IF(E23="","Falta decidir",IF(E23="Sim","OK",IF(F23="","Falta a justificativa",IF(G23="","Falta avaliar o efeito",IF(G23="Sim","Exclusão indevida",IF(D23="Quase sempre se aplica","Justificativa reforçada: requisito fora dos candidatos comuns","OK"))))))</f>
         <v>Falta decidir</v>
       </c>
     </row>
@@ -3057,7 +3057,7 @@
       <c r="F24" s="5"/>
       <c r="G24" s="19"/>
       <c r="H24" s="9" t="str">
-        <f aca="false">IF(E24="","Falta decidir",IF(E24="Sim","OK",IF(D24="Aplica-se sempre","Requisito que se aplica sempre",IF(F24="","Falta a justificativa",IF(G24="","Falta avaliar o efeito",IF(G24="Sim","Exclusão indevida","OK"))))))</f>
+        <f aca="false">IF(E24="","Falta decidir",IF(E24="Sim","OK",IF(F24="","Falta a justificativa",IF(G24="","Falta avaliar o efeito",IF(G24="Sim","Exclusão indevida",IF(D24="Quase sempre se aplica","Justificativa reforçada: requisito fora dos candidatos comuns","OK"))))))</f>
         <v>Falta decidir</v>
       </c>
     </row>
@@ -3075,7 +3075,7 @@
       <c r="F25" s="5"/>
       <c r="G25" s="19"/>
       <c r="H25" s="9" t="str">
-        <f aca="false">IF(E25="","Falta decidir",IF(E25="Sim","OK",IF(D25="Aplica-se sempre","Requisito que se aplica sempre",IF(F25="","Falta a justificativa",IF(G25="","Falta avaliar o efeito",IF(G25="Sim","Exclusão indevida","OK"))))))</f>
+        <f aca="false">IF(E25="","Falta decidir",IF(E25="Sim","OK",IF(F25="","Falta a justificativa",IF(G25="","Falta avaliar o efeito",IF(G25="Sim","Exclusão indevida",IF(D25="Quase sempre se aplica","Justificativa reforçada: requisito fora dos candidatos comuns","OK"))))))</f>
         <v>Falta decidir</v>
       </c>
     </row>
@@ -3093,7 +3093,7 @@
       <c r="F26" s="5"/>
       <c r="G26" s="19"/>
       <c r="H26" s="9" t="str">
-        <f aca="false">IF(E26="","Falta decidir",IF(E26="Sim","OK",IF(D26="Aplica-se sempre","Requisito que se aplica sempre",IF(F26="","Falta a justificativa",IF(G26="","Falta avaliar o efeito",IF(G26="Sim","Exclusão indevida","OK"))))))</f>
+        <f aca="false">IF(E26="","Falta decidir",IF(E26="Sim","OK",IF(F26="","Falta a justificativa",IF(G26="","Falta avaliar o efeito",IF(G26="Sim","Exclusão indevida",IF(D26="Quase sempre se aplica","Justificativa reforçada: requisito fora dos candidatos comuns","OK"))))))</f>
         <v>Falta decidir</v>
       </c>
     </row>
@@ -3111,7 +3111,7 @@
       <c r="F27" s="5"/>
       <c r="G27" s="19"/>
       <c r="H27" s="9" t="str">
-        <f aca="false">IF(E27="","Falta decidir",IF(E27="Sim","OK",IF(D27="Aplica-se sempre","Requisito que se aplica sempre",IF(F27="","Falta a justificativa",IF(G27="","Falta avaliar o efeito",IF(G27="Sim","Exclusão indevida","OK"))))))</f>
+        <f aca="false">IF(E27="","Falta decidir",IF(E27="Sim","OK",IF(F27="","Falta a justificativa",IF(G27="","Falta avaliar o efeito",IF(G27="Sim","Exclusão indevida",IF(D27="Quase sempre se aplica","Justificativa reforçada: requisito fora dos candidatos comuns","OK"))))))</f>
         <v>Falta decidir</v>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       <c r="F28" s="5"/>
       <c r="G28" s="19"/>
       <c r="H28" s="9" t="str">
-        <f aca="false">IF(E28="","Falta decidir",IF(E28="Sim","OK",IF(D28="Aplica-se sempre","Requisito que se aplica sempre",IF(F28="","Falta a justificativa",IF(G28="","Falta avaliar o efeito",IF(G28="Sim","Exclusão indevida","OK"))))))</f>
+        <f aca="false">IF(E28="","Falta decidir",IF(E28="Sim","OK",IF(F28="","Falta a justificativa",IF(G28="","Falta avaliar o efeito",IF(G28="Sim","Exclusão indevida",IF(D28="Quase sempre se aplica","Justificativa reforçada: requisito fora dos candidatos comuns","OK"))))))</f>
         <v>Falta decidir</v>
       </c>
     </row>
@@ -3147,7 +3147,7 @@
       <c r="F29" s="5"/>
       <c r="G29" s="19"/>
       <c r="H29" s="9" t="str">
-        <f aca="false">IF(E29="","Falta decidir",IF(E29="Sim","OK",IF(D29="Aplica-se sempre","Requisito que se aplica sempre",IF(F29="","Falta a justificativa",IF(G29="","Falta avaliar o efeito",IF(G29="Sim","Exclusão indevida","OK"))))))</f>
+        <f aca="false">IF(E29="","Falta decidir",IF(E29="Sim","OK",IF(F29="","Falta a justificativa",IF(G29="","Falta avaliar o efeito",IF(G29="Sim","Exclusão indevida",IF(D29="Quase sempre se aplica","Justificativa reforçada: requisito fora dos candidatos comuns","OK"))))))</f>
         <v>Falta decidir</v>
       </c>
     </row>
@@ -3165,7 +3165,7 @@
       <c r="F30" s="5"/>
       <c r="G30" s="19"/>
       <c r="H30" s="9" t="str">
-        <f aca="false">IF(E30="","Falta decidir",IF(E30="Sim","OK",IF(D30="Aplica-se sempre","Requisito que se aplica sempre",IF(F30="","Falta a justificativa",IF(G30="","Falta avaliar o efeito",IF(G30="Sim","Exclusão indevida","OK"))))))</f>
+        <f aca="false">IF(E30="","Falta decidir",IF(E30="Sim","OK",IF(F30="","Falta a justificativa",IF(G30="","Falta avaliar o efeito",IF(G30="Sim","Exclusão indevida",IF(D30="Quase sempre se aplica","Justificativa reforçada: requisito fora dos candidatos comuns","OK"))))))</f>
         <v>Falta decidir</v>
       </c>
     </row>
@@ -3183,7 +3183,7 @@
       <c r="F31" s="5"/>
       <c r="G31" s="19"/>
       <c r="H31" s="9" t="str">
-        <f aca="false">IF(E31="","Falta decidir",IF(E31="Sim","OK",IF(D31="Aplica-se sempre","Requisito que se aplica sempre",IF(F31="","Falta a justificativa",IF(G31="","Falta avaliar o efeito",IF(G31="Sim","Exclusão indevida","OK"))))))</f>
+        <f aca="false">IF(E31="","Falta decidir",IF(E31="Sim","OK",IF(F31="","Falta a justificativa",IF(G31="","Falta avaliar o efeito",IF(G31="Sim","Exclusão indevida",IF(D31="Quase sempre se aplica","Justificativa reforçada: requisito fora dos candidatos comuns","OK"))))))</f>
         <v>Falta decidir</v>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       <c r="F32" s="5"/>
       <c r="G32" s="19"/>
       <c r="H32" s="9" t="str">
-        <f aca="false">IF(E32="","Falta decidir",IF(E32="Sim","OK",IF(D32="Aplica-se sempre","Requisito que se aplica sempre",IF(F32="","Falta a justificativa",IF(G32="","Falta avaliar o efeito",IF(G32="Sim","Exclusão indevida","OK"))))))</f>
+        <f aca="false">IF(E32="","Falta decidir",IF(E32="Sim","OK",IF(F32="","Falta a justificativa",IF(G32="","Falta avaliar o efeito",IF(G32="Sim","Exclusão indevida",IF(D32="Quase sempre se aplica","Justificativa reforçada: requisito fora dos candidatos comuns","OK"))))))</f>
         <v>Falta decidir</v>
       </c>
     </row>
@@ -3219,7 +3219,7 @@
       <c r="F33" s="5"/>
       <c r="G33" s="19"/>
       <c r="H33" s="9" t="str">
-        <f aca="false">IF(E33="","Falta decidir",IF(E33="Sim","OK",IF(D33="Aplica-se sempre","Requisito que se aplica sempre",IF(F33="","Falta a justificativa",IF(G33="","Falta avaliar o efeito",IF(G33="Sim","Exclusão indevida","OK"))))))</f>
+        <f aca="false">IF(E33="","Falta decidir",IF(E33="Sim","OK",IF(F33="","Falta a justificativa",IF(G33="","Falta avaliar o efeito",IF(G33="Sim","Exclusão indevida",IF(D33="Quase sempre se aplica","Justificativa reforçada: requisito fora dos candidatos comuns","OK"))))))</f>
         <v>Falta decidir</v>
       </c>
     </row>
@@ -3237,7 +3237,7 @@
       <c r="F34" s="5"/>
       <c r="G34" s="19"/>
       <c r="H34" s="9" t="str">
-        <f aca="false">IF(E34="","Falta decidir",IF(E34="Sim","OK",IF(D34="Aplica-se sempre","Requisito que se aplica sempre",IF(F34="","Falta a justificativa",IF(G34="","Falta avaliar o efeito",IF(G34="Sim","Exclusão indevida","OK"))))))</f>
+        <f aca="false">IF(E34="","Falta decidir",IF(E34="Sim","OK",IF(F34="","Falta a justificativa",IF(G34="","Falta avaliar o efeito",IF(G34="Sim","Exclusão indevida",IF(D34="Quase sempre se aplica","Justificativa reforçada: requisito fora dos candidatos comuns","OK"))))))</f>
         <v>Falta decidir</v>
       </c>
     </row>
@@ -3255,7 +3255,7 @@
       <c r="F35" s="5"/>
       <c r="G35" s="19"/>
       <c r="H35" s="9" t="str">
-        <f aca="false">IF(E35="","Falta decidir",IF(E35="Sim","OK",IF(D35="Aplica-se sempre","Requisito que se aplica sempre",IF(F35="","Falta a justificativa",IF(G35="","Falta avaliar o efeito",IF(G35="Sim","Exclusão indevida","OK"))))))</f>
+        <f aca="false">IF(E35="","Falta decidir",IF(E35="Sim","OK",IF(F35="","Falta a justificativa",IF(G35="","Falta avaliar o efeito",IF(G35="Sim","Exclusão indevida",IF(D35="Quase sempre se aplica","Justificativa reforçada: requisito fora dos candidatos comuns","OK"))))))</f>
         <v>Falta decidir</v>
       </c>
     </row>
@@ -3273,7 +3273,7 @@
       <c r="F36" s="5"/>
       <c r="G36" s="19"/>
       <c r="H36" s="9" t="str">
-        <f aca="false">IF(E36="","Falta decidir",IF(E36="Sim","OK",IF(D36="Aplica-se sempre","Requisito que se aplica sempre",IF(F36="","Falta a justificativa",IF(G36="","Falta avaliar o efeito",IF(G36="Sim","Exclusão indevida","OK"))))))</f>
+        <f aca="false">IF(E36="","Falta decidir",IF(E36="Sim","OK",IF(F36="","Falta a justificativa",IF(G36="","Falta avaliar o efeito",IF(G36="Sim","Exclusão indevida",IF(D36="Quase sempre se aplica","Justificativa reforçada: requisito fora dos candidatos comuns","OK"))))))</f>
         <v>Falta decidir</v>
       </c>
     </row>
@@ -3291,7 +3291,7 @@
       <c r="F37" s="5"/>
       <c r="G37" s="19"/>
       <c r="H37" s="9" t="str">
-        <f aca="false">IF(E37="","Falta decidir",IF(E37="Sim","OK",IF(D37="Aplica-se sempre","Requisito que se aplica sempre",IF(F37="","Falta a justificativa",IF(G37="","Falta avaliar o efeito",IF(G37="Sim","Exclusão indevida","OK"))))))</f>
+        <f aca="false">IF(E37="","Falta decidir",IF(E37="Sim","OK",IF(F37="","Falta a justificativa",IF(G37="","Falta avaliar o efeito",IF(G37="Sim","Exclusão indevida",IF(D37="Quase sempre se aplica","Justificativa reforçada: requisito fora dos candidatos comuns","OK"))))))</f>
         <v>Falta decidir</v>
       </c>
     </row>
@@ -3309,7 +3309,7 @@
       <c r="F38" s="5"/>
       <c r="G38" s="19"/>
       <c r="H38" s="9" t="str">
-        <f aca="false">IF(E38="","Falta decidir",IF(E38="Sim","OK",IF(D38="Aplica-se sempre","Requisito que se aplica sempre",IF(F38="","Falta a justificativa",IF(G38="","Falta avaliar o efeito",IF(G38="Sim","Exclusão indevida","OK"))))))</f>
+        <f aca="false">IF(E38="","Falta decidir",IF(E38="Sim","OK",IF(F38="","Falta a justificativa",IF(G38="","Falta avaliar o efeito",IF(G38="Sim","Exclusão indevida",IF(D38="Quase sempre se aplica","Justificativa reforçada: requisito fora dos candidatos comuns","OK"))))))</f>
         <v>Falta decidir</v>
       </c>
     </row>
@@ -3327,7 +3327,7 @@
       <c r="F39" s="5"/>
       <c r="G39" s="19"/>
       <c r="H39" s="9" t="str">
-        <f aca="false">IF(E39="","Falta decidir",IF(E39="Sim","OK",IF(D39="Aplica-se sempre","Requisito que se aplica sempre",IF(F39="","Falta a justificativa",IF(G39="","Falta avaliar o efeito",IF(G39="Sim","Exclusão indevida","OK"))))))</f>
+        <f aca="false">IF(E39="","Falta decidir",IF(E39="Sim","OK",IF(F39="","Falta a justificativa",IF(G39="","Falta avaliar o efeito",IF(G39="Sim","Exclusão indevida",IF(D39="Quase sempre se aplica","Justificativa reforçada: requisito fora dos candidatos comuns","OK"))))))</f>
         <v>Falta decidir</v>
       </c>
     </row>
@@ -3345,7 +3345,7 @@
       <c r="F40" s="5"/>
       <c r="G40" s="19"/>
       <c r="H40" s="9" t="str">
-        <f aca="false">IF(E40="","Falta decidir",IF(E40="Sim","OK",IF(D40="Aplica-se sempre","Requisito que se aplica sempre",IF(F40="","Falta a justificativa",IF(G40="","Falta avaliar o efeito",IF(G40="Sim","Exclusão indevida","OK"))))))</f>
+        <f aca="false">IF(E40="","Falta decidir",IF(E40="Sim","OK",IF(F40="","Falta a justificativa",IF(G40="","Falta avaliar o efeito",IF(G40="Sim","Exclusão indevida",IF(D40="Quase sempre se aplica","Justificativa reforçada: requisito fora dos candidatos comuns","OK"))))))</f>
         <v>Falta decidir</v>
       </c>
     </row>
@@ -3363,7 +3363,7 @@
       <c r="F41" s="5"/>
       <c r="G41" s="19"/>
       <c r="H41" s="9" t="str">
-        <f aca="false">IF(E41="","Falta decidir",IF(E41="Sim","OK",IF(D41="Aplica-se sempre","Requisito que se aplica sempre",IF(F41="","Falta a justificativa",IF(G41="","Falta avaliar o efeito",IF(G41="Sim","Exclusão indevida","OK"))))))</f>
+        <f aca="false">IF(E41="","Falta decidir",IF(E41="Sim","OK",IF(F41="","Falta a justificativa",IF(G41="","Falta avaliar o efeito",IF(G41="Sim","Exclusão indevida",IF(D41="Quase sempre se aplica","Justificativa reforçada: requisito fora dos candidatos comuns","OK"))))))</f>
         <v>Falta decidir</v>
       </c>
     </row>
@@ -3381,7 +3381,7 @@
       <c r="F42" s="5"/>
       <c r="G42" s="19"/>
       <c r="H42" s="9" t="str">
-        <f aca="false">IF(E42="","Falta decidir",IF(E42="Sim","OK",IF(D42="Aplica-se sempre","Requisito que se aplica sempre",IF(F42="","Falta a justificativa",IF(G42="","Falta avaliar o efeito",IF(G42="Sim","Exclusão indevida","OK"))))))</f>
+        <f aca="false">IF(E42="","Falta decidir",IF(E42="Sim","OK",IF(F42="","Falta a justificativa",IF(G42="","Falta avaliar o efeito",IF(G42="Sim","Exclusão indevida",IF(D42="Quase sempre se aplica","Justificativa reforçada: requisito fora dos candidatos comuns","OK"))))))</f>
         <v>Falta decidir</v>
       </c>
     </row>
@@ -3399,7 +3399,7 @@
       <c r="F43" s="5"/>
       <c r="G43" s="19"/>
       <c r="H43" s="9" t="str">
-        <f aca="false">IF(E43="","Falta decidir",IF(E43="Sim","OK",IF(D43="Aplica-se sempre","Requisito que se aplica sempre",IF(F43="","Falta a justificativa",IF(G43="","Falta avaliar o efeito",IF(G43="Sim","Exclusão indevida","OK"))))))</f>
+        <f aca="false">IF(E43="","Falta decidir",IF(E43="Sim","OK",IF(F43="","Falta a justificativa",IF(G43="","Falta avaliar o efeito",IF(G43="Sim","Exclusão indevida",IF(D43="Quase sempre se aplica","Justificativa reforçada: requisito fora dos candidatos comuns","OK"))))))</f>
         <v>Falta decidir</v>
       </c>
     </row>
@@ -3417,7 +3417,7 @@
       <c r="F44" s="5"/>
       <c r="G44" s="19"/>
       <c r="H44" s="9" t="str">
-        <f aca="false">IF(E44="","Falta decidir",IF(E44="Sim","OK",IF(D44="Aplica-se sempre","Requisito que se aplica sempre",IF(F44="","Falta a justificativa",IF(G44="","Falta avaliar o efeito",IF(G44="Sim","Exclusão indevida","OK"))))))</f>
+        <f aca="false">IF(E44="","Falta decidir",IF(E44="Sim","OK",IF(F44="","Falta a justificativa",IF(G44="","Falta avaliar o efeito",IF(G44="Sim","Exclusão indevida",IF(D44="Quase sempre se aplica","Justificativa reforçada: requisito fora dos candidatos comuns","OK"))))))</f>
         <v>Falta decidir</v>
       </c>
     </row>
@@ -3435,7 +3435,7 @@
       <c r="F45" s="5"/>
       <c r="G45" s="19"/>
       <c r="H45" s="9" t="str">
-        <f aca="false">IF(E45="","Falta decidir",IF(E45="Sim","OK",IF(D45="Aplica-se sempre","Requisito que se aplica sempre",IF(F45="","Falta a justificativa",IF(G45="","Falta avaliar o efeito",IF(G45="Sim","Exclusão indevida","OK"))))))</f>
+        <f aca="false">IF(E45="","Falta decidir",IF(E45="Sim","OK",IF(F45="","Falta a justificativa",IF(G45="","Falta avaliar o efeito",IF(G45="Sim","Exclusão indevida",IF(D45="Quase sempre se aplica","Justificativa reforçada: requisito fora dos candidatos comuns","OK"))))))</f>
         <v>Falta decidir</v>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       <c r="F46" s="5"/>
       <c r="G46" s="19"/>
       <c r="H46" s="9" t="str">
-        <f aca="false">IF(E46="","Falta decidir",IF(E46="Sim","OK",IF(D46="Aplica-se sempre","Requisito que se aplica sempre",IF(F46="","Falta a justificativa",IF(G46="","Falta avaliar o efeito",IF(G46="Sim","Exclusão indevida","OK"))))))</f>
+        <f aca="false">IF(E46="","Falta decidir",IF(E46="Sim","OK",IF(F46="","Falta a justificativa",IF(G46="","Falta avaliar o efeito",IF(G46="Sim","Exclusão indevida",IF(D46="Quase sempre se aplica","Justificativa reforçada: requisito fora dos candidatos comuns","OK"))))))</f>
         <v>Falta decidir</v>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       <c r="F47" s="5"/>
       <c r="G47" s="19"/>
       <c r="H47" s="9" t="str">
-        <f aca="false">IF(E47="","Falta decidir",IF(E47="Sim","OK",IF(D47="Aplica-se sempre","Requisito que se aplica sempre",IF(F47="","Falta a justificativa",IF(G47="","Falta avaliar o efeito",IF(G47="Sim","Exclusão indevida","OK"))))))</f>
+        <f aca="false">IF(E47="","Falta decidir",IF(E47="Sim","OK",IF(F47="","Falta a justificativa",IF(G47="","Falta avaliar o efeito",IF(G47="Sim","Exclusão indevida",IF(D47="Quase sempre se aplica","Justificativa reforçada: requisito fora dos candidatos comuns","OK"))))))</f>
         <v>Falta decidir</v>
       </c>
     </row>
@@ -3489,7 +3489,7 @@
       <c r="F48" s="5"/>
       <c r="G48" s="19"/>
       <c r="H48" s="9" t="str">
-        <f aca="false">IF(E48="","Falta decidir",IF(E48="Sim","OK",IF(D48="Aplica-se sempre","Requisito que se aplica sempre",IF(F48="","Falta a justificativa",IF(G48="","Falta avaliar o efeito",IF(G48="Sim","Exclusão indevida","OK"))))))</f>
+        <f aca="false">IF(E48="","Falta decidir",IF(E48="Sim","OK",IF(F48="","Falta a justificativa",IF(G48="","Falta avaliar o efeito",IF(G48="Sim","Exclusão indevida",IF(D48="Quase sempre se aplica","Justificativa reforçada: requisito fora dos candidatos comuns","OK"))))))</f>
         <v>Falta decidir</v>
       </c>
     </row>
@@ -3507,7 +3507,7 @@
       <c r="F49" s="5"/>
       <c r="G49" s="19"/>
       <c r="H49" s="9" t="str">
-        <f aca="false">IF(E49="","Falta decidir",IF(E49="Sim","OK",IF(D49="Aplica-se sempre","Requisito que se aplica sempre",IF(F49="","Falta a justificativa",IF(G49="","Falta avaliar o efeito",IF(G49="Sim","Exclusão indevida","OK"))))))</f>
+        <f aca="false">IF(E49="","Falta decidir",IF(E49="Sim","OK",IF(F49="","Falta a justificativa",IF(G49="","Falta avaliar o efeito",IF(G49="Sim","Exclusão indevida",IF(D49="Quase sempre se aplica","Justificativa reforçada: requisito fora dos candidatos comuns","OK"))))))</f>
         <v>Falta decidir</v>
       </c>
     </row>
@@ -3525,7 +3525,7 @@
       <c r="F50" s="5"/>
       <c r="G50" s="19"/>
       <c r="H50" s="9" t="str">
-        <f aca="false">IF(E50="","Falta decidir",IF(E50="Sim","OK",IF(D50="Aplica-se sempre","Requisito que se aplica sempre",IF(F50="","Falta a justificativa",IF(G50="","Falta avaliar o efeito",IF(G50="Sim","Exclusão indevida","OK"))))))</f>
+        <f aca="false">IF(E50="","Falta decidir",IF(E50="Sim","OK",IF(F50="","Falta a justificativa",IF(G50="","Falta avaliar o efeito",IF(G50="Sim","Exclusão indevida",IF(D50="Quase sempre se aplica","Justificativa reforçada: requisito fora dos candidatos comuns","OK"))))))</f>
         <v>Falta decidir</v>
       </c>
     </row>
@@ -3543,7 +3543,7 @@
       <c r="F51" s="5"/>
       <c r="G51" s="19"/>
       <c r="H51" s="9" t="str">
-        <f aca="false">IF(E51="","Falta decidir",IF(E51="Sim","OK",IF(D51="Aplica-se sempre","Requisito que se aplica sempre",IF(F51="","Falta a justificativa",IF(G51="","Falta avaliar o efeito",IF(G51="Sim","Exclusão indevida","OK"))))))</f>
+        <f aca="false">IF(E51="","Falta decidir",IF(E51="Sim","OK",IF(F51="","Falta a justificativa",IF(G51="","Falta avaliar o efeito",IF(G51="Sim","Exclusão indevida",IF(D51="Quase sempre se aplica","Justificativa reforçada: requisito fora dos candidatos comuns","OK"))))))</f>
         <v>Falta decidir</v>
       </c>
     </row>
@@ -3592,7 +3592,7 @@
       </c>
       <c r="C56" s="12"/>
       <c r="D56" s="14" t="str">
-        <f aca="false">IF(COUNTA(E7:E51)=0,"Decida a aplicabilidade de cada requisito",IF(COUNTIF(H7:H51,"Exclusão indevida")+COUNTIF(H7:H51,"Requisito que se aplica sempre")&gt;0,"Há requisito declarado não aplicável que se aplica",IF(SUMPRODUCT((H7:H51&lt;&gt;"OK")*1)&gt;0,"Há requisito a decidir ou a completar","OK")))</f>
+        <f aca="false">IF(COUNTA(E7:E51)=0,"Decida a aplicabilidade de cada requisito",IF(COUNTIF(H7:H51,"Exclusão indevida")&gt;0,"Há requisito declarado não aplicável que se aplica",IF(SUMPRODUCT((H7:H51&lt;&gt;"OK")*(H7:H51&lt;&gt;"Justificativa reforçada: requisito fora dos candidatos comuns"))&gt;0,"Há requisito a decidir ou a completar",IF(COUNTIF(H7:H51,"Justificativa reforçada: requisito fora dos candidatos comuns")&gt;0,"Há requisito fora dos candidatos comuns: confira a justificativa reforçada","OK"))))</f>
         <v>Decida a aplicabilidade de cada requisito</v>
       </c>
       <c r="E56" s="14"/>
@@ -3627,8 +3627,8 @@
     <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
       <formula>H7="Exclusão indevida"</formula>
     </cfRule>
-    <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
-      <formula>H7="Requisito que se aplica sempre"</formula>
+    <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+      <formula>H7="Justificativa reforçada: requisito fora dos candidatos comuns"</formula>
     </cfRule>
     <cfRule type="expression" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>LEN(H7)&gt;0</formula>
@@ -4212,7 +4212,7 @@
         <v>224</v>
       </c>
       <c r="C10" s="21" t="n">
-        <f aca="false">COUNTIF(Aplicabilidade!H7:H51,"Exclusão indevida")+COUNTIF(Aplicabilidade!H7:H51,"Requisito que se aplica sempre")</f>
+        <f aca="false">COUNTIF(Aplicabilidade!H7:H51,"Exclusão indevida")</f>
         <v>0</v>
       </c>
       <c r="D10" s="22" t="s">
@@ -4226,7 +4226,7 @@
         <v>226</v>
       </c>
       <c r="C11" s="21" t="n">
-        <f aca="false">SUMPRODUCT((Aplicabilidade!H7:H51&lt;&gt;"OK")*1)-COUNTIF(Aplicabilidade!H7:H51,"Exclusão indevida")-COUNTIF(Aplicabilidade!H7:H51,"Requisito que se aplica sempre")</f>
+        <f aca="false">SUMPRODUCT((Aplicabilidade!H7:H51&lt;&gt;"OK")*(Aplicabilidade!H7:H51&lt;&gt;"Justificativa reforçada: requisito fora dos candidatos comuns"))-COUNTIF(Aplicabilidade!H7:H51,"Exclusão indevida")</f>
         <v>45</v>
       </c>
       <c r="D11" s="22" t="s">
@@ -5275,7 +5275,7 @@
       </c>
       <c r="I22" s="33"/>
       <c r="J22" s="9" t="str">
-        <f aca="false">IF(F22="","Falta decidir",IF(F22="Sim","OK",IF(E22="Aplica-se sempre","Requisito que se aplica sempre",IF(D22="","Falta a justificativa",IF(G22="","Falta avaliar o efeito",IF(G22="Sim","Exclusão indevida","OK"))))))</f>
+        <f aca="false">IF(F22="","Falta decidir",IF(F22="Sim","OK",IF(D22="","Falta a justificativa",IF(G22="","Falta avaliar o efeito",IF(G22="Sim","Exclusão indevida",IF(E22="Quase sempre se aplica","Justificativa reforçada: requisito fora dos candidatos comuns","OK"))))))</f>
         <v>Exclusão indevida</v>
       </c>
       <c r="K22" s="9"/>
@@ -5304,7 +5304,7 @@
       </c>
       <c r="I23" s="33"/>
       <c r="J23" s="9" t="str">
-        <f aca="false">IF(F23="","Falta decidir",IF(F23="Sim","OK",IF(E23="Aplica-se sempre","Requisito que se aplica sempre",IF(D23="","Falta a justificativa",IF(G23="","Falta avaliar o efeito",IF(G23="Sim","Exclusão indevida","OK"))))))</f>
+        <f aca="false">IF(F23="","Falta decidir",IF(F23="Sim","OK",IF(D23="","Falta a justificativa",IF(G23="","Falta avaliar o efeito",IF(G23="Sim","Exclusão indevida",IF(E23="Quase sempre se aplica","Justificativa reforçada: requisito fora dos candidatos comuns","OK"))))))</f>
         <v>Exclusão indevida</v>
       </c>
       <c r="K23" s="9"/>
@@ -5447,19 +5447,19 @@
         <v>309</v>
       </c>
       <c r="E30" s="32" t="s">
-        <v>299</v>
+        <v>310</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="G30" s="32" t="s">
         <v>230</v>
       </c>
       <c r="H30" s="7" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="I30" s="7" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="J30" s="35" t="n">
         <v>46507</v>
@@ -5474,13 +5474,13 @@
         <v>5</v>
       </c>
       <c r="C31" s="30" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="E31" s="32" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="F31" s="7" t="s">
         <v>300</v>
@@ -5504,7 +5504,7 @@
         <v>129</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E32" s="32" t="s">
         <v>306</v>
@@ -5514,10 +5514,10 @@
         <v>230</v>
       </c>
       <c r="H32" s="7" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="I32" s="7" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="J32" s="35" t="n">
         <v>46477</v>
@@ -5532,16 +5532,16 @@
         <v>7</v>
       </c>
       <c r="C33" s="30" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="E33" s="32" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="G33" s="32" t="s">
         <v>228</v>
@@ -5559,13 +5559,13 @@
         <v>8</v>
       </c>
       <c r="C34" s="30" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E34" s="32" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="F34" s="7"/>
       <c r="G34" s="32" t="s">
@@ -5584,13 +5584,13 @@
         <v>9</v>
       </c>
       <c r="C35" s="30" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="E35" s="32" t="s">
-        <v>327</v>
+        <v>310</v>
       </c>
       <c r="F35" s="7" t="s">
         <v>328</v>
@@ -5765,8 +5765,8 @@
     <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
       <formula>$J22="Exclusão indevida"</formula>
     </cfRule>
-    <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
-      <formula>$J22="Requisito que se aplica sempre"</formula>
+    <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+      <formula>$J22="Justificativa reforçada: requisito fora dos candidatos comuns"</formula>
     </cfRule>
     <cfRule type="expression" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>LEN($J22)&gt;0</formula>
@@ -5779,8 +5779,8 @@
     <cfRule type="expression" priority="9" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
       <formula>$J23="Exclusão indevida"</formula>
     </cfRule>
-    <cfRule type="expression" priority="10" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
-      <formula>$J23="Requisito que se aplica sempre"</formula>
+    <cfRule type="expression" priority="10" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+      <formula>$J23="Justificativa reforçada: requisito fora dos candidatos comuns"</formula>
     </cfRule>
     <cfRule type="expression" priority="11" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>LEN($J23)&gt;0</formula>
@@ -6180,7 +6180,7 @@
       </c>
       <c r="I22" s="33"/>
       <c r="J22" s="9" t="str">
-        <f aca="false">IF(F22="","Falta decidir",IF(F22="Sim","OK",IF(E22="Aplica-se sempre","Requisito que se aplica sempre",IF(D22="","Falta a justificativa",IF(G22="","Falta avaliar o efeito",IF(G22="Sim","Exclusão indevida","OK"))))))</f>
+        <f aca="false">IF(F22="","Falta decidir",IF(F22="Sim","OK",IF(D22="","Falta a justificativa",IF(G22="","Falta avaliar o efeito",IF(G22="Sim","Exclusão indevida",IF(E22="Quase sempre se aplica","Justificativa reforçada: requisito fora dos candidatos comuns","OK"))))))</f>
         <v>OK</v>
       </c>
       <c r="K22" s="9"/>
@@ -6242,7 +6242,7 @@
         <v>346</v>
       </c>
       <c r="E26" s="32" t="s">
-        <v>327</v>
+        <v>310</v>
       </c>
       <c r="F26" s="7" t="s">
         <v>347</v>
@@ -6296,7 +6296,7 @@
         <v>349</v>
       </c>
       <c r="E28" s="32" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="F28" s="7" t="s">
         <v>350</v>
@@ -6323,7 +6323,7 @@
         <v>351</v>
       </c>
       <c r="E29" s="32" t="s">
-        <v>327</v>
+        <v>310</v>
       </c>
       <c r="F29" s="7" t="s">
         <v>352</v>
@@ -6339,18 +6339,18 @@
         <v>OK</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B30" s="16" t="n">
         <v>5</v>
       </c>
       <c r="C30" s="30" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D30" s="7" t="s">
         <v>353</v>
       </c>
       <c r="E30" s="32" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="F30" s="7" t="s">
         <v>347</v>
@@ -6404,7 +6404,7 @@
         <v>7</v>
       </c>
       <c r="C32" s="30" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D32" s="7" t="s">
         <v>358</v>
@@ -6413,7 +6413,7 @@
         <v>356</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="G32" s="32" t="s">
         <v>228</v>
@@ -6431,13 +6431,13 @@
         <v>8</v>
       </c>
       <c r="C33" s="30" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D33" s="7" t="s">
         <v>359</v>
       </c>
       <c r="E33" s="32" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="F33" s="7" t="s">
         <v>360</v>
@@ -6464,13 +6464,13 @@
         <v>9</v>
       </c>
       <c r="C34" s="30" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D34" s="7" t="s">
         <v>363</v>
       </c>
       <c r="E34" s="32" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="F34" s="7" t="s">
         <v>364</v>
@@ -6497,7 +6497,7 @@
         <v>365</v>
       </c>
       <c r="E35" s="32" t="s">
-        <v>327</v>
+        <v>310</v>
       </c>
       <c r="F35" s="7"/>
       <c r="G35" s="32" t="s">
@@ -6645,8 +6645,8 @@
     <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
       <formula>$J22="Exclusão indevida"</formula>
     </cfRule>
-    <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
-      <formula>$J22="Requisito que se aplica sempre"</formula>
+    <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+      <formula>$J22="Justificativa reforçada: requisito fora dos candidatos comuns"</formula>
     </cfRule>
     <cfRule type="expression" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>LEN($J22)&gt;0</formula>
